--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential All Seasons Bond Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential All Seasons Bond Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="245">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential All Seasons Bond Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,30 +70,96 @@
     <t>SOV</t>
   </si>
   <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
     <t>IN0020200120</t>
   </si>
   <si>
     <t>IN0020210137</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>IN0020240118</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN0020250018</t>
+  </si>
+  <si>
+    <t>State Government of Chhattisgarh</t>
+  </si>
+  <si>
+    <t>IN3520240083</t>
+  </si>
+  <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
+  </si>
+  <si>
+    <t>IN0020240142</t>
+  </si>
+  <si>
+    <t>IN0020230077</t>
+  </si>
+  <si>
+    <t>IN0020240134</t>
   </si>
   <si>
     <t>IN0020220151</t>
   </si>
   <si>
-    <t>IN0020230077</t>
-  </si>
-  <si>
-    <t>IN0020240126</t>
-  </si>
-  <si>
-    <t>IN0020240134</t>
+    <t>^</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd. **</t>
+  </si>
+  <si>
+    <t>INE205A08038</t>
+  </si>
+  <si>
+    <t>ICRA AA</t>
+  </si>
+  <si>
+    <t>Godrej Properties Ltd. **</t>
+  </si>
+  <si>
+    <t>INE484J08089</t>
+  </si>
+  <si>
+    <t>ICRA AA+</t>
+  </si>
+  <si>
     <t>Nirma Ltd. **</t>
   </si>
   <si>
@@ -103,15 +169,6 @@
     <t>CRISIL AA</t>
   </si>
   <si>
-    <t>Godrej Properties Ltd. **</t>
-  </si>
-  <si>
-    <t>INE484J08089</t>
-  </si>
-  <si>
-    <t>ICRA AA+</t>
-  </si>
-  <si>
     <t>Oberoi Realty Ltd. **</t>
   </si>
   <si>
@@ -121,6 +178,15 @@
     <t>CARE AA+</t>
   </si>
   <si>
+    <t>Tata Projects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE725H08246</t>
+  </si>
+  <si>
+    <t>FITCH AA</t>
+  </si>
+  <si>
     <t>Bharti Telecom Ltd. **</t>
   </si>
   <si>
@@ -130,6 +196,12 @@
     <t>CRISIL AA+</t>
   </si>
   <si>
+    <t>Cholamandalam Investment And Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE121A08PP7</t>
+  </si>
+  <si>
     <t>SEIL Energy India Ltd. **</t>
   </si>
   <si>
@@ -145,124 +217,301 @@
     <t>CARE AA-</t>
   </si>
   <si>
-    <t>NABARD</t>
-  </si>
-  <si>
-    <t>INE261F08DO9</t>
-  </si>
-  <si>
-    <t>CRISIL AAA</t>
-  </si>
-  <si>
     <t>Macrotech Developers Ltd. **</t>
   </si>
   <si>
     <t>INE670K07273</t>
   </si>
   <si>
+    <t>Aptus Value Housing Finance India Ltd. **</t>
+  </si>
+  <si>
+    <t>INE852O07139</t>
+  </si>
+  <si>
+    <t>INE852O07147</t>
+  </si>
+  <si>
+    <t>360 One Prime Ltd.</t>
+  </si>
+  <si>
+    <t>INE248U07EQ0</t>
+  </si>
+  <si>
+    <t>Manappuram Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE522D07CH7</t>
+  </si>
+  <si>
+    <t>Tata Realty &amp; Infrastructure Ltd. **</t>
+  </si>
+  <si>
+    <t>INE371K08219</t>
+  </si>
+  <si>
+    <t>Ess Kay Fincorp Ltd **</t>
+  </si>
+  <si>
+    <t>INE124N07721</t>
+  </si>
+  <si>
+    <t>ICRA AA-</t>
+  </si>
+  <si>
+    <t>Eris Lifesciences Ltd. **</t>
+  </si>
+  <si>
+    <t>INE406M08029</t>
+  </si>
+  <si>
+    <t>INE406M08011</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE414G07JF9</t>
+  </si>
+  <si>
+    <t>INE414G07IQ8</t>
+  </si>
+  <si>
+    <t>Avanse Financial Services Ltd **</t>
+  </si>
+  <si>
+    <t>INE087P07444</t>
+  </si>
+  <si>
     <t>CRISIL AA-</t>
   </si>
   <si>
-    <t>Aptus Value Housing Finance India Ltd. **</t>
-  </si>
-  <si>
-    <t>INE852O07139</t>
-  </si>
-  <si>
-    <t>INE852O07147</t>
+    <t>Motilal oswal finvest Ltd **</t>
+  </si>
+  <si>
+    <t>INE01WN07094</t>
+  </si>
+  <si>
+    <t>TMF Holdings Ltd. **</t>
+  </si>
+  <si>
+    <t>INE909H08378</t>
+  </si>
+  <si>
+    <t>Indostar Capital Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE896L07AJ8</t>
+  </si>
+  <si>
+    <t>TVS Credit Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE729N08089</t>
+  </si>
+  <si>
+    <t>INE121A08PT9</t>
+  </si>
+  <si>
+    <t>The Great Eastern Shipping Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE017A08268</t>
+  </si>
+  <si>
+    <t>Aadhar Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE883F07397</t>
+  </si>
+  <si>
+    <t>CARE AA</t>
+  </si>
+  <si>
+    <t>INE909H08337</t>
+  </si>
+  <si>
+    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE128M08078</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(CE)</t>
+  </si>
+  <si>
+    <t>JM Financial Products Ltd. **</t>
+  </si>
+  <si>
+    <t>INE523H07CB9</t>
+  </si>
+  <si>
+    <t>Godrej Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE233A08071</t>
+  </si>
+  <si>
+    <t>Hampi Expressways Private Ltd. **</t>
+  </si>
+  <si>
+    <t>INE03ST08010</t>
+  </si>
+  <si>
+    <t>CARE AA+(CE)</t>
+  </si>
+  <si>
+    <t>INE729N08097</t>
+  </si>
+  <si>
+    <t>Altius Telecom Infrastructure Trust. **</t>
+  </si>
+  <si>
+    <t>INE0BWS08019</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Home Finance Ltd **</t>
+  </si>
+  <si>
+    <t>INE658R07430</t>
   </si>
   <si>
     <t>360 One Prime Ltd. **</t>
   </si>
   <si>
-    <t>INE248U07EQ0</t>
-  </si>
-  <si>
-    <t>IIFL Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE477L07AW0</t>
-  </si>
-  <si>
-    <t>Tata Realty &amp; Infrastructure Ltd. **</t>
-  </si>
-  <si>
-    <t>INE371K08219</t>
-  </si>
-  <si>
-    <t>Manappuram Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE522D07CH7</t>
-  </si>
-  <si>
-    <t>Ess Kay Fincorp Ltd **</t>
-  </si>
-  <si>
-    <t>INE124N07721</t>
-  </si>
-  <si>
-    <t>ICRA AA-</t>
-  </si>
-  <si>
-    <t>Eris Lifesciences Ltd. **</t>
-  </si>
-  <si>
-    <t>INE406M08029</t>
-  </si>
-  <si>
-    <t>FITCH AA-</t>
-  </si>
-  <si>
-    <t>INE406M08011</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G07JF9</t>
-  </si>
-  <si>
-    <t>INE414G07IQ8</t>
-  </si>
-  <si>
-    <t>INE896L07876</t>
-  </si>
-  <si>
-    <t>Motilal oswal finvest Ltd **</t>
-  </si>
-  <si>
-    <t>INE01WN07094</t>
-  </si>
-  <si>
-    <t>Avanse Financial Services Ltd **</t>
-  </si>
-  <si>
-    <t>INE087P07444</t>
-  </si>
-  <si>
-    <t>INE261F08DX0</t>
-  </si>
-  <si>
-    <t>INE477L07AV2</t>
-  </si>
-  <si>
-    <t>TMF Holdings Ltd. **</t>
-  </si>
-  <si>
-    <t>INE909H08378</t>
-  </si>
-  <si>
-    <t>TVS Credit Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE729N08089</t>
-  </si>
-  <si>
-    <t>The Great Eastern Shipping Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE017A08268</t>
+    <t>INE248U07FN4</t>
+  </si>
+  <si>
+    <t>JM Financial Asset Recosntruction Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE265J07514</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd. **</t>
+  </si>
+  <si>
+    <t>INE775A08089</t>
+  </si>
+  <si>
+    <t>FITCH AAA</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd. **</t>
+  </si>
+  <si>
+    <t>INE813H07192</t>
+  </si>
+  <si>
+    <t>INE729N08030</t>
+  </si>
+  <si>
+    <t>Aavas Financiers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE216P07217</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India.</t>
+  </si>
+  <si>
+    <t>INE556F08KS8</t>
+  </si>
+  <si>
+    <t>INE403D08181</t>
+  </si>
+  <si>
+    <t>Bahadur Chand Investments Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE087M08134</t>
+  </si>
+  <si>
+    <t>INE403D08157</t>
+  </si>
+  <si>
+    <t>INE087M08126</t>
+  </si>
+  <si>
+    <t>Jodhpur Wind Farms Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE03IQ08033</t>
+  </si>
+  <si>
+    <t>CRISIL AA+(CE)</t>
+  </si>
+  <si>
+    <t>Sheela Foam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE916U08012</t>
+  </si>
+  <si>
+    <t>INE017A08235</t>
+  </si>
+  <si>
+    <t>INE916U08038</t>
+  </si>
+  <si>
+    <t>DME Development Ltd. **</t>
+  </si>
+  <si>
+    <t>INE0J7Q07108</t>
+  </si>
+  <si>
+    <t>INE523H07BZ0</t>
+  </si>
+  <si>
+    <t>Oriental Nagpur Betul Highway Ltd. **</t>
+  </si>
+  <si>
+    <t>INE105N07191</t>
+  </si>
+  <si>
+    <t>INE916U08020</t>
+  </si>
+  <si>
+    <t>INE0J7Q07017</t>
+  </si>
+  <si>
+    <t>INE0J7Q07074</t>
+  </si>
+  <si>
+    <t>INE0J7Q07082</t>
+  </si>
+  <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
+    <t>INE0J7Q07066</t>
+  </si>
+  <si>
+    <t>INE0J7Q07041</t>
+  </si>
+  <si>
+    <t>INE0J7Q07090</t>
+  </si>
+  <si>
+    <t>INE729N08063</t>
+  </si>
+  <si>
+    <t>INE105N07183</t>
+  </si>
+  <si>
+    <t>Rural Electrification Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE020B08BS3</t>
+  </si>
+  <si>
+    <t>INE883F07330</t>
   </si>
   <si>
     <t>Tata Capital Housing Finance Ltd. **</t>
@@ -271,237 +520,6 @@
     <t>INE033L07HZ9</t>
   </si>
   <si>
-    <t>Samvardhana Motherson International Ltd. **</t>
-  </si>
-  <si>
-    <t>INE775A08089</t>
-  </si>
-  <si>
-    <t>FITCH AAA</t>
-  </si>
-  <si>
-    <t>INE909H08337</t>
-  </si>
-  <si>
-    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE128M08078</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(CE)</t>
-  </si>
-  <si>
-    <t>JM Financial Products Ltd. **</t>
-  </si>
-  <si>
-    <t>INE523H07CB9</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08071</t>
-  </si>
-  <si>
-    <t>Hampi Expressways Private Ltd. **</t>
-  </si>
-  <si>
-    <t>INE03ST08010</t>
-  </si>
-  <si>
-    <t>CARE AA+(CE)</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE658R08180</t>
-  </si>
-  <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
-    <t>INE729N08097</t>
-  </si>
-  <si>
-    <t>JM Financial Asset Recosntruction Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE265J07514</t>
-  </si>
-  <si>
-    <t>Altius Telecom Infrastructure Trust. **</t>
-  </si>
-  <si>
-    <t>INE0BWS08019</t>
-  </si>
-  <si>
-    <t>INE265J07522</t>
-  </si>
-  <si>
-    <t>INE248U07FN4</t>
-  </si>
-  <si>
-    <t>ICRA AA</t>
-  </si>
-  <si>
-    <t>INE403D08157</t>
-  </si>
-  <si>
-    <t>Tata Motors Finance Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE477S08100</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Home Finance Ltd **</t>
-  </si>
-  <si>
-    <t>INE658R07430</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India.</t>
-  </si>
-  <si>
-    <t>INE556F08KJ7</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd. **</t>
-  </si>
-  <si>
-    <t>INE813H07192</t>
-  </si>
-  <si>
-    <t>INE729N08030</t>
-  </si>
-  <si>
-    <t>Aavas Financiers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE216P07217</t>
-  </si>
-  <si>
-    <t>CARE AA</t>
-  </si>
-  <si>
-    <t>INE017A08243</t>
-  </si>
-  <si>
-    <t>AU Small Finance Bank Ltd.( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE949L08418</t>
-  </si>
-  <si>
-    <t>INE403D08181</t>
-  </si>
-  <si>
-    <t>INE896L07868</t>
-  </si>
-  <si>
-    <t>Bahadur Chand Investments Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE087M08126</t>
-  </si>
-  <si>
-    <t>INE087M08134</t>
-  </si>
-  <si>
-    <t>Jodhpur Wind Farms Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE03IQ08033</t>
-  </si>
-  <si>
-    <t>CRISIL AA+(CE)</t>
-  </si>
-  <si>
-    <t>DME Development Ltd. **</t>
-  </si>
-  <si>
-    <t>INE0J7Q07108</t>
-  </si>
-  <si>
-    <t>Sheela Foam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE916U08012</t>
-  </si>
-  <si>
-    <t>INE916U08038</t>
-  </si>
-  <si>
-    <t>INE017A08235</t>
-  </si>
-  <si>
-    <t>INE916U08046</t>
-  </si>
-  <si>
-    <t>INE523H07BZ0</t>
-  </si>
-  <si>
-    <t>INE916U08020</t>
-  </si>
-  <si>
-    <t>Oriental Nagpur Betul Highway Ltd. **</t>
-  </si>
-  <si>
-    <t>INE105N07191</t>
-  </si>
-  <si>
-    <t>INE0J7Q07017</t>
-  </si>
-  <si>
-    <t>INE0J7Q07074</t>
-  </si>
-  <si>
-    <t>INE0J7Q07082</t>
-  </si>
-  <si>
-    <t>INE0J7Q07066</t>
-  </si>
-  <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
-    <t>INE0J7Q07041</t>
-  </si>
-  <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
-    <t>INE0J7Q07090</t>
-  </si>
-  <si>
-    <t>INE729N08063</t>
-  </si>
-  <si>
-    <t>INE813H07135</t>
-  </si>
-  <si>
-    <t>INE105N07183</t>
-  </si>
-  <si>
-    <t>Rural Electrification Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE020B08BS3</t>
-  </si>
-  <si>
-    <t>Aadhar Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE883F07330</t>
-  </si>
-  <si>
-    <t>INE105N07175</t>
-  </si>
-  <si>
     <t>NABARD **</t>
   </si>
   <si>
@@ -550,66 +568,78 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A16FU3</t>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A16ZQ5</t>
   </si>
   <si>
     <t>CRISIL A1+</t>
   </si>
   <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A16EU1</t>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A16NQ8</t>
+  </si>
+  <si>
+    <t>Union Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE692A16IF6</t>
+  </si>
+  <si>
+    <t>ICRA A1+</t>
+  </si>
+  <si>
+    <t>Punjab National Bank **</t>
+  </si>
+  <si>
+    <t>INE160A16QM3</t>
+  </si>
+  <si>
+    <t>INE692A16II0</t>
+  </si>
+  <si>
+    <t>Canara Bank **</t>
+  </si>
+  <si>
+    <t>INE476A16ZW3</t>
+  </si>
+  <si>
+    <t>INE692A16HY9</t>
+  </si>
+  <si>
+    <t>INE476A16ZA9</t>
+  </si>
+  <si>
+    <t>INE476A16ZP7</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE237A160Z6</t>
+  </si>
+  <si>
+    <t>Punjab National Bank</t>
+  </si>
+  <si>
+    <t>INE160A16QL5</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda **</t>
+  </si>
+  <si>
+    <t>INE028A16GQ4</t>
   </si>
   <si>
     <t>FITCH A1+</t>
   </si>
   <si>
-    <t>Punjab National Bank **</t>
-  </si>
-  <si>
-    <t>INE160A16OL0</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE238AD6819</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A16MR8</t>
-  </si>
-  <si>
-    <t>INE556F16AR4</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda **</t>
-  </si>
-  <si>
-    <t>INE028A16GT8</t>
-  </si>
-  <si>
-    <t>INE028A16EX5</t>
-  </si>
-  <si>
-    <t>INE160A16OP1</t>
-  </si>
-  <si>
-    <t>INE238AD6827</t>
-  </si>
-  <si>
     <t>Commercial Papers</t>
   </si>
   <si>
-    <t>INE556F14KR8</t>
-  </si>
-  <si>
     <t>Bills Rediscounted</t>
   </si>
   <si>
@@ -637,12 +667,66 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>GSCCIL- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -22-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -22-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> ICICI Securities Primary Dealership Ltd.- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
     <t>** Non Traded / Illiquid Securities.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
@@ -652,7 +736,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -665,20 +749,17 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY Composite Debt
-Index  A-III</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="\^"/>
+    <numFmt numFmtId="180" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -756,7 +837,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -842,6 +923,14 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -868,7 +957,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -923,7 +1012,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -932,6 +1021,10 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -946,6 +1039,9 @@
       <protection/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1046,13 +1142,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>189</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>165</xdr:row>
+      <xdr:row>199</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1070,8 +1166,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30451425"/>
-          <a:ext cx="4210050" cy="1905000"/>
+          <a:off x="666750" y="36976050"/>
+          <a:ext cx="6419850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1085,13 +1181,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>170</xdr:row>
+      <xdr:row>204</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>180</xdr:row>
+      <xdr:row>214</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1109,8 +1205,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="33308925"/>
-          <a:ext cx="4210050" cy="1905000"/>
+          <a:off x="666750" y="39833550"/>
+          <a:ext cx="6419850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1443,19 +1539,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J169"/>
+  <dimension ref="B1:J202"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="63.142857142857146" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.571428571428571" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="24" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="24" width="96.28571428571429" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="24" width="17.0" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="24" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="24" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="24" width="12.571428571428571" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="24" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="24" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="24" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="24" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1543,10 +1639,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1154620.6399999997</v>
+        <v>1238640.7499999998</v>
       </c>
       <c r="H5" s="10">
-        <v>0.8527498543853</v>
+        <v>0.8267859908897</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1580,10 +1676,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1147105.64</v>
+        <v>1231867.4999999998</v>
       </c>
       <c r="H7" s="10">
-        <v>0.8471996200194001</v>
+        <v>0.8222648832055</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1617,10 +1713,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>643798.87</v>
+        <v>622916.84</v>
       </c>
       <c r="H9" s="10">
-        <v>0.4754803210935</v>
+        <v>0.4157936163517</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1643,16 +1739,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>499431490</v>
+        <v>198132590</v>
       </c>
       <c r="G10" s="16">
-        <v>511449.81</v>
+        <v>208867.41</v>
       </c>
       <c r="H10" s="17">
-        <v>0.3777333748383</v>
+        <v>0.1394178647378</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1666,22 +1762,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>7.930000000000001</v>
+        <v>7.34</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="15">
-        <v>66848050</v>
+        <v>118212000</v>
       </c>
       <c r="G11" s="16">
-        <v>68560.43</v>
+        <v>125828.87</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0506355894516</v>
+        <v>0.0839900891085</v>
       </c>
       <c r="I11" s="16">
-        <v>7.66</v>
+        <v>6.98</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1695,22 +1791,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="14">
-        <v>7.53</v>
+        <v>7.81</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>45460800</v>
+        <v>66848050</v>
       </c>
       <c r="G12" s="16">
-        <v>45792.07</v>
+        <v>69417.82</v>
       </c>
       <c r="H12" s="17">
-        <v>0.033819922901</v>
+        <v>0.0463360188128</v>
       </c>
       <c r="I12" s="16">
-        <v>7.47</v>
+        <v>7.31</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1724,22 +1820,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>7.18</v>
+        <v>6.99</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>11732700</v>
+        <v>45460800</v>
       </c>
       <c r="G13" s="16">
-        <v>12053.53</v>
+        <v>46404.75</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0089021844892</v>
+        <v>0.0309749192499</v>
       </c>
       <c r="I13" s="16">
-        <v>6.87</v>
+        <v>6.80</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1753,22 +1849,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="14">
-        <v>7.26</v>
+        <v>6.79</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>3314200</v>
+        <v>36083000</v>
       </c>
       <c r="G14" s="16">
-        <v>3417.64</v>
+        <v>37379.43</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0025241121727</v>
+        <v>0.0249505670402</v>
       </c>
       <c r="I14" s="16">
-        <v>6.86</v>
+        <v>6.37</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1782,22 +1878,22 @@
         <v>22</v>
       </c>
       <c r="D15" s="14">
-        <v>7.18</v>
+        <v>7.09</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="15">
-        <v>2100000</v>
+        <v>30000000</v>
       </c>
       <c r="G15" s="16">
-        <v>2159.25</v>
+        <v>30999.39</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0015947230278</v>
+        <v>0.0206919249009</v>
       </c>
       <c r="I15" s="16">
-        <v>6.96</v>
+        <v>6.94</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1805,28 +1901,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="14">
-        <v>6.79</v>
+        <v>7.12</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="15">
-        <v>185000</v>
+        <v>26457100</v>
       </c>
       <c r="G16" s="16">
-        <v>186.22</v>
+        <v>27347.09</v>
       </c>
       <c r="H16" s="17">
-        <v>0.000137533552</v>
+        <v>0.0182540344355</v>
       </c>
       <c r="I16" s="16">
-        <v>6.81</v>
+        <v>6.83</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1834,28 +1930,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="14">
-        <v>6.92</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="15">
-        <v>178350</v>
+        <v>24000000</v>
       </c>
       <c r="G17" s="16">
-        <v>179.92</v>
+        <v>24906.12</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0001328806609</v>
+        <v>0.0166247001832</v>
       </c>
       <c r="I17" s="16">
-        <v>6.94</v>
+        <v>6.82</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1863,36 +1959,57 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="14">
+        <v>6.90</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="15">
+        <v>20000000</v>
+      </c>
+      <c r="G18" s="16">
+        <v>20134.64</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0.0134397631304</v>
+      </c>
+      <c r="I18" s="16">
+        <v>6.97</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
-      <c r="B19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="9">
-        <v>492924.15000000014</v>
-      </c>
-      <c r="H19" s="10">
-        <v>0.3640511719355998</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>13</v>
+      <c r="B19" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="14">
+        <v>7.32</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="15">
+        <v>11051200</v>
+      </c>
+      <c r="G19" s="16">
+        <v>11599.64</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0.0077426968646</v>
+      </c>
+      <c r="I19" s="16">
+        <v>6.81</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1900,28 +2017,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>8.50</v>
+        <v>7.13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F20" s="15">
-        <v>20000</v>
+        <v>10982600</v>
       </c>
       <c r="G20" s="16">
-        <v>20164.76</v>
+        <v>11344.48</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0148927669903</v>
+        <v>0.0075723789468</v>
       </c>
       <c r="I20" s="16">
-        <v>8.04</v>
+        <v>6.75</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1929,28 +2046,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D21" s="14">
-        <v>8.40</v>
+        <v>7.29</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F21" s="15">
-        <v>20000</v>
+        <v>3466000</v>
       </c>
       <c r="G21" s="16">
-        <v>20086.76</v>
+        <v>3618.02</v>
       </c>
       <c r="H21" s="17">
-        <v>0.0148351597674</v>
+        <v>0.0024150087511</v>
       </c>
       <c r="I21" s="16">
-        <v>8.22</v>
+        <v>6.88</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -1958,28 +2075,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="14">
-        <v>8.05</v>
+        <v>7.09</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F22" s="15">
-        <v>20000</v>
+        <v>2500000</v>
       </c>
       <c r="G22" s="16">
-        <v>19923.28</v>
+        <v>2575.27</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0147144209365</v>
+        <v>0.0017189787747</v>
       </c>
       <c r="I22" s="16">
-        <v>8.55</v>
+        <v>6.99</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1987,28 +2104,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D23" s="14">
-        <v>8.950000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F23" s="15">
-        <v>16000</v>
+        <v>2100000</v>
       </c>
       <c r="G23" s="16">
-        <v>16151.22</v>
+        <v>2236.57</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0119285504052</v>
+        <v>0.0014928983594</v>
       </c>
       <c r="I23" s="16">
-        <v>8.35</v>
+        <v>6.50</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -2016,28 +2133,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>8.45</v>
+        <v>6.92</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F24" s="15">
-        <v>15000</v>
+        <v>178350</v>
       </c>
       <c r="G24" s="16">
-        <v>14898.68</v>
+        <v>186.74</v>
       </c>
       <c r="H24" s="17">
-        <v>0.0110034818021</v>
+        <v>0.0001246479384</v>
       </c>
       <c r="I24" s="16">
-        <v>8.74</v>
+        <v>6.52</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -2045,28 +2162,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>7.26</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F25" s="15">
-        <v>15000</v>
+        <v>66400</v>
       </c>
       <c r="G25" s="16">
-        <v>14884.79</v>
-      </c>
-      <c r="H25" s="17">
-        <v>0.0109932232851</v>
+        <v>70.6</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="I25" s="16">
-        <v>10.44</v>
+        <v>6.31</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -2074,57 +2191,36 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="14">
-        <v>7.40</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="15">
-        <v>1300</v>
-      </c>
-      <c r="G26" s="16">
-        <v>12960.65</v>
-      </c>
-      <c r="H26" s="17">
-        <v>0.0095721417211</v>
-      </c>
-      <c r="I26" s="16">
-        <v>7.72</v>
+        <v>13</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
-      <c r="B27" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="14">
-        <v>8.60</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="15">
-        <v>12500</v>
-      </c>
-      <c r="G27" s="16">
-        <v>12471.16</v>
-      </c>
-      <c r="H27" s="17">
-        <v>0.0092106268549</v>
-      </c>
-      <c r="I27" s="16">
-        <v>9.03</v>
+      <c r="B27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="9">
+        <v>598191.2199999999</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.39928939893789994</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -2132,28 +2228,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D28" s="14">
-        <v>8.75</v>
+        <v>7.58</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" s="15">
-        <v>12500</v>
+        <v>94000</v>
       </c>
       <c r="G28" s="16">
-        <v>12379.86</v>
+        <v>96350.09</v>
       </c>
       <c r="H28" s="17">
-        <v>0.0091431968619</v>
+        <v>0.0643131631454</v>
       </c>
       <c r="I28" s="16">
-        <v>9.90</v>
+        <v>7.21</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -2161,28 +2257,28 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D29" s="14">
-        <v>8.75</v>
+        <v>9.40</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F29" s="15">
-        <v>12500</v>
+        <v>40000</v>
       </c>
       <c r="G29" s="16">
-        <v>12361.75</v>
+        <v>40184.96</v>
       </c>
       <c r="H29" s="17">
-        <v>0.0091298216464</v>
+        <v>0.0268232431176</v>
       </c>
       <c r="I29" s="16">
-        <v>9.88</v>
+        <v>9.06</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -2190,28 +2286,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D30" s="14">
-        <v>9.41</v>
+        <v>8.40</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F30" s="15">
-        <v>1200000</v>
+        <v>20000</v>
       </c>
       <c r="G30" s="16">
-        <v>12007.14</v>
+        <v>20556.36</v>
       </c>
       <c r="H30" s="17">
-        <v>0.0088679229626</v>
+        <v>0.0137212589459</v>
       </c>
       <c r="I30" s="16">
-        <v>9.34</v>
+        <v>7.22</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -2219,28 +2315,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D31" s="14">
         <v>8.50</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F31" s="15">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="G31" s="16">
-        <v>11953.96</v>
+        <v>20333.26</v>
       </c>
       <c r="H31" s="17">
-        <v>0.0088286466534</v>
+        <v>0.0135723409045</v>
       </c>
       <c r="I31" s="16">
-        <v>9.25</v>
+        <v>7.40</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
@@ -2248,28 +2344,28 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D32" s="14">
-        <v>8.25</v>
+        <v>8.05</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F32" s="15">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="G32" s="16">
-        <v>11024.13</v>
+        <v>20308.74</v>
       </c>
       <c r="H32" s="17">
-        <v>0.008141916857</v>
+        <v>0.0135559739373</v>
       </c>
       <c r="I32" s="16">
-        <v>8.01</v>
+        <v>7.76</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -2277,28 +2373,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D33" s="14">
-        <v>9.10</v>
+        <v>8.60</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F33" s="15">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="G33" s="16">
-        <v>10996.69</v>
+        <v>20191.08</v>
       </c>
       <c r="H33" s="17">
-        <v>0.0081216509314</v>
+        <v>0.0134774365246</v>
       </c>
       <c r="I33" s="16">
-        <v>9.05</v>
+        <v>7.93</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2306,28 +2402,28 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D34" s="14">
-        <v>9.25</v>
+        <v>8.950000000000001</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F34" s="15">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="G34" s="16">
-        <v>10911.08</v>
+        <v>16287.82</v>
       </c>
       <c r="H34" s="17">
-        <v>0.0080584233114</v>
+        <v>0.0108720316186</v>
       </c>
       <c r="I34" s="16">
-        <v>9.77</v>
+        <v>7.59</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -2335,28 +2431,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D35" s="14">
-        <v>8.73</v>
+        <v>9.10</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F35" s="15">
-        <v>10450</v>
+        <v>15000</v>
       </c>
       <c r="G35" s="16">
-        <v>10490.80</v>
+        <v>15389.48</v>
       </c>
       <c r="H35" s="17">
-        <v>0.0077480237772</v>
+        <v>0.010272394535</v>
       </c>
       <c r="I35" s="16">
-        <v>8.50</v>
+        <v>8.53</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2364,28 +2460,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="D36" s="14">
-        <v>8.73</v>
+        <v>8.45</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F36" s="15">
-        <v>10050</v>
+        <v>15000</v>
       </c>
       <c r="G36" s="16">
-        <v>10082.63</v>
+        <v>15162.99</v>
       </c>
       <c r="H36" s="17">
-        <v>0.0074465681337</v>
+        <v>0.0101212136869</v>
       </c>
       <c r="I36" s="16">
-        <v>8.53</v>
+        <v>7.85</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2393,28 +2489,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D37" s="14">
-        <v>9.02</v>
+        <v>10</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F37" s="15">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="G37" s="16">
-        <v>10067.17</v>
+        <v>15068.07</v>
       </c>
       <c r="H37" s="17">
-        <v>0.0074351500867</v>
+        <v>0.010057855101</v>
       </c>
       <c r="I37" s="16">
-        <v>8.66</v>
+        <v>9.60</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2425,25 +2521,25 @@
         <v>67</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D38" s="14">
-        <v>8.85</v>
+        <v>8.60</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F38" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G38" s="16">
-        <v>10031.42</v>
+        <v>12641.86</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0074087467761</v>
+        <v>0.0084383730689</v>
       </c>
       <c r="I38" s="16">
-        <v>8.63</v>
+        <v>8.05</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2451,28 +2547,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D39" s="14">
-        <v>9.950000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F39" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G39" s="16">
-        <v>10021.03</v>
+        <v>12447.89</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0074010731986</v>
+        <v>0.0083088991446</v>
       </c>
       <c r="I39" s="16">
-        <v>9.50</v>
+        <v>9.55</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2480,28 +2576,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="D40" s="14">
-        <v>9.50</v>
+        <v>8.75</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="F40" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G40" s="16">
-        <v>10013.91</v>
+        <v>12435.48</v>
       </c>
       <c r="H40" s="17">
-        <v>0.0073958146931</v>
+        <v>0.0083006155368</v>
       </c>
       <c r="I40" s="16">
-        <v>8.93</v>
+        <v>9.55</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2509,28 +2605,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="D41" s="14">
-        <v>9.40</v>
+        <v>9.41</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F41" s="15">
-        <v>10000</v>
+        <v>1200000</v>
       </c>
       <c r="G41" s="16">
-        <v>9994.71</v>
+        <v>12046.51</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0073816344536</v>
+        <v>0.0080409801689</v>
       </c>
       <c r="I41" s="16">
-        <v>9.66</v>
+        <v>8.50</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2538,28 +2634,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>75</v>
       </c>
       <c r="D42" s="14">
-        <v>7.58</v>
+        <v>9.10</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F42" s="15">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G42" s="16">
-        <v>9986.22</v>
+        <v>11109.87</v>
       </c>
       <c r="H42" s="17">
-        <v>0.007375364129</v>
+        <v>0.0074157780427</v>
       </c>
       <c r="I42" s="16">
-        <v>7.63</v>
+        <v>8.15</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2567,28 +2663,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D43" s="14">
-        <v>8.50</v>
+        <v>8.25</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F43" s="15">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G43" s="16">
-        <v>9984.3</v>
+        <v>11089.14</v>
       </c>
       <c r="H43" s="17">
-        <v>0.007373946105</v>
+        <v>0.00740194088</v>
       </c>
       <c r="I43" s="16">
-        <v>9.2</v>
+        <v>7.04</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2596,28 +2692,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D44" s="14">
-        <v>7.9926</v>
+        <v>9.25</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F44" s="15">
-        <v>1000</v>
+        <v>11000</v>
       </c>
       <c r="G44" s="16">
-        <v>9942.12</v>
+        <v>10973.39</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0073427938914</v>
+        <v>0.007324678382</v>
       </c>
       <c r="I44" s="16">
-        <v>8.41</v>
+        <v>9.41</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2625,28 +2721,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D45" s="14">
-        <v>9.50</v>
+        <v>8.73</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F45" s="15">
-        <v>80</v>
+        <v>10450</v>
       </c>
       <c r="G45" s="16">
-        <v>8172.06</v>
+        <v>10660.90</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0060355087494</v>
+        <v>0.0071160929997</v>
       </c>
       <c r="I45" s="16">
-        <v>8.64</v>
+        <v>7.61</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2657,25 +2753,25 @@
         <v>81</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D46" s="14">
-        <v>8.24</v>
+        <v>8.73</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F46" s="15">
-        <v>750</v>
+        <v>10050</v>
       </c>
       <c r="G46" s="16">
-        <v>7450.58</v>
+        <v>10214.61</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0055026567081</v>
+        <v>0.0068181968423</v>
       </c>
       <c r="I46" s="16">
-        <v>8.62</v>
+        <v>7.60</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2683,28 +2779,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" s="14">
-        <v>7.9613000000000005</v>
+        <v>9.02</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F47" s="15">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="G47" s="16">
-        <v>7016.19</v>
+        <v>10181.44</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0051818361751</v>
+        <v>0.006796056047</v>
       </c>
       <c r="I47" s="16">
-        <v>7.80</v>
+        <v>8.04</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2712,28 +2808,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D48" s="14">
-        <v>8.15</v>
+        <v>8.85</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F48" s="15">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="G48" s="16">
-        <v>7015.40</v>
+        <v>10104.44</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0051812527173</v>
+        <v>0.0067446589641</v>
       </c>
       <c r="I48" s="16">
-        <v>7.89</v>
+        <v>8.03</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2741,28 +2837,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>88</v>
       </c>
       <c r="D49" s="14">
-        <v>7.750500000000001</v>
+        <v>9.40</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="F49" s="15">
-        <v>700</v>
+        <v>10000</v>
       </c>
       <c r="G49" s="16">
-        <v>6958.47</v>
+        <v>10042.76</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0051392068301</v>
+        <v>0.0067034878982</v>
       </c>
       <c r="I49" s="16">
-        <v>8.45</v>
+        <v>9.21</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2770,28 +2866,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D50" s="14">
-        <v>6.58</v>
+        <v>9.50</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="F50" s="15">
-        <v>700</v>
+        <v>10000</v>
       </c>
       <c r="G50" s="16">
-        <v>6892.64</v>
+        <v>10036.10</v>
       </c>
       <c r="H50" s="17">
-        <v>0.005090587811</v>
+        <v>0.0066990423843</v>
       </c>
       <c r="I50" s="16">
-        <v>7.89</v>
+        <v>7.67</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2805,22 +2901,22 @@
         <v>93</v>
       </c>
       <c r="D51" s="14">
-        <v>8.92</v>
+        <v>7.9926</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F51" s="15">
-        <v>6200</v>
+        <v>1000</v>
       </c>
       <c r="G51" s="16">
-        <v>6189.82</v>
+        <v>10000.61</v>
       </c>
       <c r="H51" s="17">
-        <v>0.00457151719</v>
+        <v>0.0066753530015</v>
       </c>
       <c r="I51" s="16">
-        <v>9.35</v>
+        <v>8</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2834,22 +2930,22 @@
         <v>95</v>
       </c>
       <c r="D52" s="14">
-        <v>8.3</v>
+        <v>9.60</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F52" s="15">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="G52" s="16">
-        <v>6009.06</v>
+        <v>9981.66</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0044380161434999996</v>
+        <v>0.0066627039792</v>
       </c>
       <c r="I52" s="16">
-        <v>8.19</v>
+        <v>9.76</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2863,22 +2959,22 @@
         <v>97</v>
       </c>
       <c r="D53" s="14">
-        <v>8.2</v>
+        <v>9.50</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="F53" s="15">
-        <v>6000</v>
+        <v>80</v>
       </c>
       <c r="G53" s="16">
-        <v>5955.01</v>
+        <v>8259.85</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0043980972922</v>
+        <v>0.0055134051312</v>
       </c>
       <c r="I53" s="16">
-        <v>8.36</v>
+        <v>8.11</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2886,28 +2982,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D54" s="14">
-        <v>7.266</v>
+        <v>9.05</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="F54" s="15">
-        <v>500</v>
+        <v>7500</v>
       </c>
       <c r="G54" s="16">
-        <v>5257.58</v>
+        <v>7676.98</v>
       </c>
       <c r="H54" s="17">
-        <v>0.003883007478</v>
+        <v>0.0051243425637</v>
       </c>
       <c r="I54" s="16">
-        <v>8.74</v>
+        <v>8.56</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2915,28 +3011,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D55" s="14">
-        <v>9.35</v>
+        <v>8.24</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F55" s="15">
-        <v>50</v>
+        <v>750</v>
       </c>
       <c r="G55" s="16">
-        <v>5107.4</v>
+        <v>7565.39</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0037720914172</v>
+        <v>0.0050498568431</v>
       </c>
       <c r="I55" s="16">
-        <v>8.64</v>
+        <v>7.53</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -2944,28 +3040,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" s="14">
+        <v>8.10</v>
+      </c>
+      <c r="E56" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="14">
-        <v>10.200000000000001</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>62</v>
-      </c>
       <c r="F56" s="15">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="G56" s="16">
-        <v>5012.96</v>
+        <v>7058.02</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0037023423642</v>
+        <v>0.0047111901166</v>
       </c>
       <c r="I56" s="16">
-        <v>9.88</v>
+        <v>7.81</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -2973,28 +3069,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D57" s="14">
-        <v>8.40</v>
+        <v>7.750500000000001</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F57" s="15">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="G57" s="16">
-        <v>5010.4</v>
+        <v>6985.69</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0037004516656</v>
+        <v>0.0046629102334</v>
       </c>
       <c r="I57" s="16">
-        <v>8.50</v>
+        <v>7.92</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -3002,28 +3098,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C58" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D58" s="14">
+        <v>6.58</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="14">
-        <v>10.200000000000001</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>62</v>
-      </c>
       <c r="F58" s="15">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="G58" s="16">
-        <v>5009.13</v>
+        <v>6984.11</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0036995137018</v>
+        <v>0.0046618555919</v>
       </c>
       <c r="I58" s="16">
-        <v>9.77</v>
+        <v>6.81</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -3031,28 +3127,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D59" s="14">
-        <v>9.50</v>
+        <v>8.92</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="F59" s="15">
-        <v>5000</v>
+        <v>6200</v>
       </c>
       <c r="G59" s="16">
-        <v>5007.74</v>
+        <v>6249.28</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0036984871115</v>
+        <v>0.0041713605475</v>
       </c>
       <c r="I59" s="16">
-        <v>9.3</v>
+        <v>8.48</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -3060,28 +3156,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D60" s="14">
-        <v>8.700000000000001</v>
+        <v>8.3</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F60" s="15">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="G60" s="16">
-        <v>5007.63</v>
+        <v>6058.79</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0036984058706</v>
+        <v>0.0040442095044</v>
       </c>
       <c r="I60" s="16">
-        <v>8.39</v>
+        <v>7.28</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -3089,28 +3185,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D61" s="14">
-        <v>7.48</v>
+        <v>8.2</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="F61" s="15">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="G61" s="16">
-        <v>4996.97</v>
+        <v>6005.29</v>
       </c>
       <c r="H61" s="17">
-        <v>0.0036905328835</v>
+        <v>0.0040084985442</v>
       </c>
       <c r="I61" s="16">
-        <v>7.86</v>
+        <v>7.42</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -3118,28 +3214,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D62" s="14">
-        <v>8.55</v>
+        <v>9.35</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="F62" s="15">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="G62" s="16">
-        <v>4995.9</v>
+        <v>5171.64</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0036897426305</v>
+        <v>0.0034520416851</v>
       </c>
       <c r="I62" s="16">
-        <v>8.59</v>
+        <v>8.11</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3147,28 +3243,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D63" s="14">
-        <v>7.55</v>
+        <v>8.40</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F63" s="15">
         <v>5000</v>
       </c>
       <c r="G63" s="16">
-        <v>4992.35</v>
+        <v>5059.87</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0036871207633</v>
+        <v>0.0033774358156</v>
       </c>
       <c r="I63" s="16">
-        <v>7.61</v>
+        <v>7.40</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3176,28 +3272,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D64" s="14">
-        <v>7.45</v>
+        <v>8.55</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F64" s="15">
-        <v>450</v>
+        <v>5000</v>
       </c>
       <c r="G64" s="16">
-        <v>4450.45</v>
+        <v>5055.50</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0032868982746</v>
+        <v>0.0033745188642</v>
       </c>
       <c r="I64" s="16">
-        <v>8.03</v>
+        <v>7.74</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3205,28 +3301,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D65" s="14">
-        <v>9.40</v>
+        <v>9.50</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F65" s="15">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="G65" s="16">
-        <v>4043.56</v>
+        <v>5040.95</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0029863879803</v>
+        <v>0.0033648068181</v>
       </c>
       <c r="I65" s="16">
-        <v>8.55</v>
+        <v>8.63</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3234,28 +3330,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D66" s="14">
-        <v>8.75</v>
+        <v>10.200000000000001</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="F66" s="15">
-        <v>340</v>
+        <v>5000</v>
       </c>
       <c r="G66" s="16">
-        <v>3421.34</v>
+        <v>5014.34</v>
       </c>
       <c r="H66" s="17">
-        <v>0.002526844823</v>
+        <v>0.0033470447872</v>
       </c>
       <c r="I66" s="16">
-        <v>8.33</v>
+        <v>8.35</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3263,28 +3359,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D67" s="14">
-        <v>8.700000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="F67" s="15">
-        <v>290</v>
+        <v>4500</v>
       </c>
       <c r="G67" s="16">
-        <v>2894.83</v>
+        <v>4528.27</v>
       </c>
       <c r="H67" s="17">
-        <v>0.0021379886825</v>
+        <v>0.0030225956953</v>
       </c>
       <c r="I67" s="16">
-        <v>8.75</v>
+        <v>6.94</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3292,28 +3388,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D68" s="14">
-        <v>10.90</v>
+        <v>7.45</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F68" s="15">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="G68" s="16">
-        <v>2513.63</v>
+        <v>4526.01</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0018564518442</v>
+        <v>0.0030210871575</v>
       </c>
       <c r="I68" s="16">
-        <v>9</v>
+        <v>7.07</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3321,28 +3417,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D69" s="14">
-        <v>8.90</v>
+        <v>9.40</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F69" s="15">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="G69" s="16">
-        <v>2507.63</v>
+        <v>4052.62</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0018520205193</v>
+        <v>0.0027051018969</v>
       </c>
       <c r="I69" s="16">
-        <v>8.39</v>
+        <v>8.01</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3350,28 +3446,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D70" s="14">
-        <v>9.950000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="F70" s="15">
-        <v>2500</v>
+        <v>340</v>
       </c>
       <c r="G70" s="16">
-        <v>2502.85</v>
+        <v>3455.74</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0018484902305</v>
+        <v>0.0023066877302</v>
       </c>
       <c r="I70" s="16">
-        <v>8.98</v>
+        <v>7.43</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3379,28 +3475,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D71" s="14">
-        <v>9.25</v>
+        <v>7.34</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="F71" s="15">
         <v>2500</v>
       </c>
       <c r="G71" s="16">
-        <v>2493.14</v>
+        <v>2555.34</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0018413188698</v>
+        <v>0.0017056756076</v>
       </c>
       <c r="I71" s="16">
-        <v>9.91</v>
+        <v>6.65</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3408,28 +3504,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D72" s="14">
-        <v>9.25</v>
+        <v>8.90</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="F72" s="15">
         <v>2500</v>
       </c>
       <c r="G72" s="16">
-        <v>2485.91</v>
+        <v>2512.2</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0018359791234</v>
+        <v>0.0016768798913</v>
       </c>
       <c r="I72" s="16">
-        <v>9.8</v>
+        <v>7.58</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3437,28 +3533,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D73" s="14">
-        <v>6.75</v>
+        <v>9.25</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="F73" s="15">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="G73" s="16">
-        <v>2462.74</v>
+        <v>2511.43</v>
       </c>
       <c r="H73" s="17">
-        <v>0.0018188668239</v>
+        <v>0.0016763659205</v>
       </c>
       <c r="I73" s="16">
-        <v>8.66</v>
+        <v>8.40</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3466,28 +3562,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D74" s="14">
-        <v>9.54</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F74" s="15">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="G74" s="16">
-        <v>2018.69</v>
+        <v>2509.91</v>
       </c>
       <c r="H74" s="17">
-        <v>0.0014909118579</v>
+        <v>0.0016753513287</v>
       </c>
       <c r="I74" s="16">
-        <v>9.43</v>
+        <v>7.58</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3495,28 +3591,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D75" s="14">
-        <v>8.45</v>
+        <v>9.25</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="F75" s="15">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G75" s="16">
-        <v>2003.81</v>
+        <v>2506.29</v>
       </c>
       <c r="H75" s="17">
-        <v>0.0014799221722</v>
+        <v>0.0016729349983</v>
       </c>
       <c r="I75" s="16">
-        <v>8.28</v>
+        <v>8</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
@@ -3524,28 +3620,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D76" s="14">
-        <v>8.45</v>
+        <v>6.75</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="F76" s="15">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="G76" s="16">
-        <v>2002.86</v>
+        <v>2489.22</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0014792205458</v>
+        <v>0.0016615408658</v>
       </c>
       <c r="I76" s="16">
-        <v>8.32</v>
+        <v>7.46</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3553,28 +3649,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D77" s="14">
-        <v>8.700000000000001</v>
+        <v>8.45</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F77" s="15">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="G77" s="16">
-        <v>1999.76</v>
+        <v>2026.17</v>
       </c>
       <c r="H77" s="17">
-        <v>0.001476931028</v>
+        <v>0.0013524574992</v>
       </c>
       <c r="I77" s="16">
-        <v>8.65</v>
+        <v>7.34</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3582,28 +3678,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D78" s="14">
-        <v>8.45</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="F78" s="15">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="G78" s="16">
-        <v>1999.46</v>
+        <v>2019.77</v>
       </c>
       <c r="H78" s="17">
-        <v>0.0014767094617</v>
+        <v>0.0013481855338</v>
       </c>
       <c r="I78" s="16">
-        <v>8.38</v>
+        <v>7.52</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3611,28 +3707,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D79" s="14">
-        <v>8.90</v>
+        <v>8.45</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F79" s="15">
         <v>2000</v>
       </c>
       <c r="G79" s="16">
-        <v>1998.58</v>
+        <v>2016.92</v>
       </c>
       <c r="H79" s="17">
-        <v>0.0014760595341</v>
+        <v>0.0013462831743</v>
       </c>
       <c r="I79" s="16">
-        <v>9.17</v>
+        <v>7.39</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3640,28 +3736,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D80" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="F80" s="15">
-        <v>2000</v>
+        <v>190</v>
       </c>
       <c r="G80" s="16">
-        <v>1997.36</v>
+        <v>2012.80</v>
       </c>
       <c r="H80" s="17">
-        <v>0.001475158498</v>
+        <v>0.0013435330966</v>
       </c>
       <c r="I80" s="16">
-        <v>8.43</v>
+        <v>8.93</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3669,28 +3765,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D81" s="14">
-        <v>8.28</v>
+        <v>8.90</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F81" s="15">
         <v>2000</v>
       </c>
       <c r="G81" s="16">
-        <v>1986.34</v>
+        <v>2010.42</v>
       </c>
       <c r="H81" s="17">
-        <v>0.0014670196314</v>
+        <v>0.0013419444595</v>
       </c>
       <c r="I81" s="16">
-        <v>9.10</v>
+        <v>8.09</v>
       </c>
       <c r="J81" s="11" t="s">
         <v>13</v>
@@ -3698,28 +3794,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D82" s="14">
-        <v>9.54</v>
+        <v>8.28</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F82" s="15">
-        <v>175</v>
+        <v>2000</v>
       </c>
       <c r="G82" s="16">
-        <v>1861.39</v>
+        <v>2006.24</v>
       </c>
       <c r="H82" s="17">
-        <v>0.0013747372916</v>
+        <v>0.0013391543321</v>
       </c>
       <c r="I82" s="16">
-        <v>9.47</v>
+        <v>8.02</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>13</v>
@@ -3727,28 +3823,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D83" s="14">
-        <v>9.54</v>
+        <v>8.45</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F83" s="15">
-        <v>175</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="16">
-        <v>1848.13</v>
+        <v>2005.07</v>
       </c>
       <c r="H83" s="17">
-        <v>0.0013649440637</v>
+        <v>0.0013383733635</v>
       </c>
       <c r="I83" s="16">
-        <v>9.28</v>
+        <v>7.30</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>13</v>
@@ -3756,28 +3852,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D84" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F84" s="15">
         <v>175</v>
       </c>
       <c r="G84" s="16">
-        <v>1846.14</v>
+        <v>1862.90</v>
       </c>
       <c r="H84" s="17">
-        <v>0.0013634743409</v>
+        <v>0.0012434756586</v>
       </c>
       <c r="I84" s="16">
-        <v>9.36</v>
+        <v>8.95</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>13</v>
@@ -3785,28 +3881,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D85" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F85" s="15">
         <v>175</v>
       </c>
       <c r="G85" s="16">
-        <v>1834.88</v>
+        <v>1850.94</v>
       </c>
       <c r="H85" s="17">
-        <v>0.0013551582213</v>
+        <v>0.0012354924234</v>
       </c>
       <c r="I85" s="16">
-        <v>9.3</v>
+        <v>8.63</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>13</v>
@@ -3814,28 +3910,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D86" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F86" s="15">
         <v>175</v>
       </c>
       <c r="G86" s="16">
-        <v>1827.44</v>
+        <v>1848.33</v>
       </c>
       <c r="H86" s="17">
-        <v>0.0013496633785</v>
+        <v>0.0012337502625</v>
       </c>
       <c r="I86" s="16">
-        <v>9.24</v>
+        <v>8.81</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
@@ -3843,28 +3939,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D87" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F87" s="15">
         <v>175</v>
       </c>
       <c r="G87" s="16">
-        <v>1819.33</v>
+        <v>1841.46</v>
       </c>
       <c r="H87" s="17">
-        <v>0.0013436737044</v>
+        <v>0.0012291645747</v>
       </c>
       <c r="I87" s="16">
-        <v>9.18</v>
+        <v>8.25</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
@@ -3872,28 +3968,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D88" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F88" s="15">
         <v>175</v>
       </c>
       <c r="G88" s="16">
-        <v>1810.48</v>
+        <v>1841.03</v>
       </c>
       <c r="H88" s="17">
-        <v>0.0013371375003</v>
+        <v>0.0012288775521</v>
       </c>
       <c r="I88" s="16">
-        <v>9.12</v>
+        <v>7.06</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
@@ -3901,28 +3997,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D89" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F89" s="15">
         <v>175</v>
       </c>
       <c r="G89" s="16">
-        <v>1800.84</v>
+        <v>1840.88</v>
       </c>
       <c r="H89" s="17">
-        <v>0.0013300178383</v>
+        <v>0.0012287774279</v>
       </c>
       <c r="I89" s="16">
-        <v>9.04</v>
+        <v>7.64</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -3930,28 +4026,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D90" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F90" s="15">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G90" s="16">
-        <v>1683.54</v>
+        <v>1840.69</v>
       </c>
       <c r="H90" s="17">
-        <v>0.0012433854377</v>
+        <v>0.0012286506039</v>
       </c>
       <c r="I90" s="16">
-        <v>9.45</v>
+        <v>8.47</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -3959,28 +4055,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D91" s="14">
-        <v>8.85</v>
+        <v>9.58</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F91" s="15">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="G91" s="16">
-        <v>1509.24</v>
+        <v>1838.72</v>
       </c>
       <c r="H91" s="17">
-        <v>0.001114655451</v>
+        <v>0.0012273356396</v>
       </c>
       <c r="I91" s="16">
-        <v>8.57</v>
+        <v>8.01</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
@@ -3988,28 +4084,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D92" s="14">
-        <v>6.50</v>
+        <v>9.58</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F92" s="15">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="G92" s="16">
-        <v>998.68</v>
+        <v>1691.61</v>
       </c>
       <c r="H92" s="17">
-        <v>0.000737579249</v>
+        <v>0.0011291405115</v>
       </c>
       <c r="I92" s="16">
-        <v>7.66</v>
+        <v>8.83</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
@@ -4017,28 +4113,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D93" s="14">
-        <v>8.28</v>
+        <v>8.85</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F93" s="15">
-        <v>820</v>
+        <v>15</v>
       </c>
       <c r="G93" s="16">
-        <v>816.37</v>
+        <v>1521.89</v>
       </c>
       <c r="H93" s="17">
-        <v>0.0006029334436</v>
+        <v>0.0010158533309</v>
       </c>
       <c r="I93" s="16">
-        <v>9.16</v>
+        <v>8.04</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -4046,28 +4142,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D94" s="14">
-        <v>8.8</v>
+        <v>8.28</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F94" s="15">
-        <v>50</v>
+        <v>820</v>
       </c>
       <c r="G94" s="16">
-        <v>524.86</v>
+        <v>821</v>
       </c>
       <c r="H94" s="17">
-        <v>0.0003876375261</v>
+        <v>0.0005480130526</v>
       </c>
       <c r="I94" s="16">
-        <v>7.39</v>
+        <v>7.79</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -4075,28 +4171,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D95" s="14">
-        <v>8.65</v>
+        <v>8.8</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="F95" s="15">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G95" s="16">
-        <v>503.86</v>
+        <v>536.84</v>
       </c>
       <c r="H95" s="17">
-        <v>0.0003721278892</v>
+        <v>0.0003583377919</v>
       </c>
       <c r="I95" s="16">
-        <v>8.33</v>
+        <v>6.62</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -4104,28 +4200,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D96" s="14">
-        <v>8.28</v>
+        <v>8.65</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F96" s="15">
         <v>500</v>
       </c>
       <c r="G96" s="16">
-        <v>499.43</v>
+        <v>509.16</v>
       </c>
       <c r="H96" s="17">
-        <v>0.0003688560943</v>
+        <v>0.0003398615418</v>
       </c>
       <c r="I96" s="16">
-        <v>8.78</v>
+        <v>7.72</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -4133,28 +4229,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D97" s="14">
-        <v>8.620000000000001</v>
+        <v>7.9613000000000005</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F97" s="15">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="G97" s="16">
-        <v>109.09</v>
+        <v>504.82</v>
       </c>
       <c r="H97" s="17">
-        <v>0.0000805688711</v>
+        <v>0.0003369646153</v>
       </c>
       <c r="I97" s="16">
-        <v>7.22</v>
+        <v>6.85</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4162,35 +4258,35 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>13</v>
+        <v>168</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D98" s="14">
+        <v>8.620000000000001</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F98" s="15">
+        <v>10</v>
+      </c>
+      <c r="G98" s="16">
+        <v>111.32</v>
+      </c>
+      <c r="H98" s="17">
+        <v>0.0000743054969</v>
+      </c>
+      <c r="I98" s="16">
+        <v>6.86</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="9">
-        <v>10382.62</v>
-      </c>
-      <c r="H99" s="10">
-        <v>0.0076681269903</v>
-      </c>
-      <c r="I99" s="9" t="s">
+      <c r="B99" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J99" s="11" t="s">
@@ -4198,29 +4294,29 @@
       </c>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F100" s="15">
-        <v>850</v>
-      </c>
-      <c r="G100" s="16">
-        <v>10382.62</v>
-      </c>
-      <c r="H100" s="17">
-        <v>0.0076681269903</v>
-      </c>
-      <c r="I100" s="16">
-        <v>8.11</v>
+      <c r="B100" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9">
+        <v>10759.44</v>
+      </c>
+      <c r="H100" s="10">
+        <v>0.0071818679159</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4228,35 +4324,35 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>13</v>
+        <v>171</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F101" s="15">
+        <v>850</v>
+      </c>
+      <c r="G101" s="16">
+        <v>10759.44</v>
+      </c>
+      <c r="H101" s="17">
+        <v>0.0071818679159</v>
+      </c>
+      <c r="I101" s="16">
+        <v>7.24</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H102" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I102" s="9" t="s">
+      <c r="B102" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J102" s="11" t="s">
@@ -4264,7 +4360,28 @@
       </c>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I103" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J103" s="11" t="s">
@@ -4272,28 +4389,7 @@
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9">
-        <v>7515</v>
-      </c>
-      <c r="H104" s="10">
-        <v>0.0055502343659</v>
-      </c>
-      <c r="I104" s="9" t="s">
+      <c r="B104" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J104" s="11" t="s">
@@ -4301,29 +4397,29 @@
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F105" s="15">
-        <v>750000000</v>
-      </c>
-      <c r="G105" s="16">
-        <v>7515</v>
-      </c>
-      <c r="H105" s="17">
-        <v>0.0055502343659</v>
-      </c>
-      <c r="I105" s="16">
-        <v>9.21</v>
+      <c r="B105" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="9">
+        <v>6773.25</v>
+      </c>
+      <c r="H105" s="10">
+        <v>0.0045211076842</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4331,35 +4427,35 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>13</v>
+        <v>176</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F106" s="15">
+        <v>750000000</v>
+      </c>
+      <c r="G106" s="16">
+        <v>6773.25</v>
+      </c>
+      <c r="H106" s="17">
+        <v>0.0045211076842</v>
+      </c>
+      <c r="I106" s="16">
+        <v>8.60</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I107" s="9" t="s">
+      <c r="B107" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J107" s="11" t="s">
@@ -4367,7 +4463,28 @@
       </c>
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I108" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J108" s="11" t="s">
@@ -4375,36 +4492,36 @@
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J109" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" ht="15" customHeight="1">
+      <c r="B110" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J109" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="12" t="s">
+      <c r="H110" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I110" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J110" s="11" t="s">
@@ -4412,28 +4529,7 @@
       </c>
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
-      <c r="B111" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I111" s="9" t="s">
+      <c r="B111" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4441,7 +4537,28 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I112" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
@@ -4449,28 +4566,7 @@
       </c>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="9">
-        <v>85633.01999999999</v>
-      </c>
-      <c r="H113" s="10">
-        <v>0.06324462148489998</v>
-      </c>
-      <c r="I113" s="9" t="s">
+      <c r="B113" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4478,7 +4574,28 @@
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="9">
+        <v>108938.19000000003</v>
+      </c>
+      <c r="H114" s="10">
+        <v>0.07271565170500001</v>
+      </c>
+      <c r="I114" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J114" s="11" t="s">
@@ -4486,28 +4603,7 @@
       </c>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" s="9">
-        <v>80671.45</v>
-      </c>
-      <c r="H115" s="10">
-        <v>0.059580233418</v>
-      </c>
-      <c r="I115" s="9" t="s">
+      <c r="B115" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
@@ -4515,29 +4611,29 @@
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F116" s="15">
-        <v>4000</v>
-      </c>
-      <c r="G116" s="16">
-        <v>19902.70</v>
-      </c>
-      <c r="H116" s="17">
-        <v>0.0146992214923</v>
-      </c>
-      <c r="I116" s="16">
-        <v>7.14</v>
+      <c r="B116" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="9">
+        <v>108938.19000000003</v>
+      </c>
+      <c r="H116" s="10">
+        <v>0.07271565170500001</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
@@ -4545,28 +4641,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F117" s="15">
-        <v>2300</v>
+        <v>4000</v>
       </c>
       <c r="G117" s="16">
-        <v>11486.21</v>
+        <v>19337.08</v>
       </c>
       <c r="H117" s="17">
-        <v>0.0084831879542</v>
+        <v>0.0129073961508</v>
       </c>
       <c r="I117" s="16">
-        <v>7.30</v>
+        <v>6.45</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4574,28 +4670,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D118" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F118" s="15">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="G118" s="16">
-        <v>9988.02</v>
+        <v>16947.30</v>
       </c>
       <c r="H118" s="17">
-        <v>0.0073766935264</v>
+        <v>0.0113122309462</v>
       </c>
       <c r="I118" s="16">
-        <v>7.30</v>
+        <v>6.40</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
@@ -4603,28 +4699,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F119" s="15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G119" s="16">
-        <v>9948.27</v>
+        <v>14508.69</v>
       </c>
       <c r="H119" s="17">
-        <v>0.0073473359994</v>
+        <v>0.0096844719812</v>
       </c>
       <c r="I119" s="16">
-        <v>7.30</v>
+        <v>6.44</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
@@ -4632,28 +4728,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F120" s="15">
         <v>2000</v>
       </c>
       <c r="G120" s="16">
-        <v>9920.85</v>
+        <v>9680.12</v>
       </c>
       <c r="H120" s="17">
-        <v>0.0073270848448</v>
+        <v>0.0064614276626</v>
       </c>
       <c r="I120" s="16">
-        <v>7.28</v>
+        <v>6.45</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>13</v>
@@ -4661,28 +4757,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F121" s="15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G121" s="16">
-        <v>7461.20</v>
+        <v>9659.28</v>
       </c>
       <c r="H121" s="17">
-        <v>0.0055105001531</v>
+        <v>0.0064475170755</v>
       </c>
       <c r="I121" s="16">
-        <v>7.30</v>
+        <v>6.44</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -4690,28 +4786,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D122" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F122" s="15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G122" s="16">
-        <v>4997</v>
+        <v>9645.47</v>
       </c>
       <c r="H122" s="17">
-        <v>0.0036905550401</v>
+        <v>0.0064382989753</v>
       </c>
       <c r="I122" s="16">
-        <v>7.30</v>
+        <v>6.45</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
@@ -4719,28 +4815,28 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F123" s="15">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G123" s="16">
-        <v>4981.20</v>
+        <v>7271.72</v>
       </c>
       <c r="H123" s="17">
-        <v>0.0036788858847</v>
+        <v>0.004853833709</v>
       </c>
       <c r="I123" s="16">
-        <v>7.25</v>
+        <v>6.44</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
@@ -4751,25 +4847,25 @@
         <v>184</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F124" s="15">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="G124" s="16">
-        <v>1488.69</v>
+        <v>4920.55</v>
       </c>
       <c r="H124" s="17">
-        <v>0.0010994781634</v>
+        <v>0.0032844404703</v>
       </c>
       <c r="I124" s="16">
-        <v>7.30</v>
+        <v>6.27</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
@@ -4777,28 +4873,28 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="C125" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>180</v>
-      </c>
       <c r="F125" s="15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G125" s="16">
-        <v>497.31</v>
+        <v>4840.06</v>
       </c>
       <c r="H125" s="17">
-        <v>0.0003672903596</v>
+        <v>0.0032307138313</v>
       </c>
       <c r="I125" s="16">
-        <v>7.30</v>
+        <v>6.45</v>
       </c>
       <c r="J125" s="11" t="s">
         <v>13</v>
@@ -4806,36 +4902,57 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
-        <v>13</v>
+        <v>200</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F126" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G126" s="16">
+        <v>4836.21</v>
+      </c>
+      <c r="H126" s="17">
+        <v>0.0032281439771</v>
+      </c>
+      <c r="I126" s="16">
+        <v>6.40</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="9">
-        <v>4961.57</v>
-      </c>
-      <c r="H127" s="10">
-        <v>0.0036643880669</v>
-      </c>
-      <c r="I127" s="9" t="s">
-        <v>13</v>
+      <c r="B127" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F127" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G127" s="16">
+        <v>4835.1</v>
+      </c>
+      <c r="H127" s="17">
+        <v>0.0032274030582</v>
+      </c>
+      <c r="I127" s="16">
+        <v>6.45</v>
       </c>
       <c r="J127" s="11" t="s">
         <v>13</v>
@@ -4843,28 +4960,28 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
       <c r="B128" s="12" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D128" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="F128" s="15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G128" s="16">
-        <v>4961.57</v>
+        <v>2456.61</v>
       </c>
       <c r="H128" s="17">
-        <v>0.0036643880669</v>
+        <v>0.0016397738675</v>
       </c>
       <c r="I128" s="16">
-        <v>7.25</v>
+        <v>6.26</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>13</v>
@@ -4880,7 +4997,7 @@
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
       <c r="B130" s="7" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>13</v>
@@ -4895,10 +5012,10 @@
         <v>13</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I130" s="9" t="s">
         <v>13</v>
@@ -4917,7 +5034,7 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
       <c r="B132" s="7" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>13</v>
@@ -4932,10 +5049,10 @@
         <v>13</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I132" s="9" t="s">
         <v>13</v>
@@ -4954,7 +5071,7 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
       <c r="B134" s="7" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>13</v>
@@ -4968,11 +5085,11 @@
       <c r="F134" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G134" s="9">
-        <v>3619.66</v>
-      </c>
-      <c r="H134" s="10">
-        <v>0.0026733148802</v>
+      <c r="G134" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="I134" s="9" t="s">
         <v>13</v>
@@ -4983,64 +5100,64 @@
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1">
       <c r="B135" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C135" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F135" s="15">
+        <v>13</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" ht="15" customHeight="1">
+      <c r="B136" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="9">
+        <v>3712.67</v>
+      </c>
+      <c r="H136" s="10">
+        <v>0.0024781871134</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J136" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" ht="15" customHeight="1">
+      <c r="B137" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F137" s="15">
         <v>33175.66</v>
       </c>
-      <c r="G135" s="16">
-        <v>3619.66</v>
-      </c>
-      <c r="H135" s="17">
-        <v>0.0026733148802</v>
-      </c>
-      <c r="I135" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J135" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" ht="15" customHeight="1">
-      <c r="B136" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J136" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" ht="15" customHeight="1">
-      <c r="B137" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G137" s="9">
-        <v>84009.05</v>
-      </c>
-      <c r="H137" s="10">
-        <v>0.0620452317177</v>
-      </c>
-      <c r="I137" s="9" t="s">
+      <c r="G137" s="16">
+        <v>3712.67</v>
+      </c>
+      <c r="H137" s="17">
+        <v>0.0024781871134</v>
+      </c>
+      <c r="I137" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J137" s="11" t="s">
@@ -5056,179 +5173,1122 @@
       </c>
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
-      <c r="B139" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E139" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F139" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G139" s="19">
-        <v>26114.50734463986</v>
-      </c>
-      <c r="H139" s="20">
-        <v>0.019286977526753037</v>
-      </c>
-      <c r="I139" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J139" s="21" t="s">
+      <c r="B139" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="9">
+        <v>118737.48</v>
+      </c>
+      <c r="H139" s="10">
+        <v>0.0792566246977</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J139" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
-      <c r="B140" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="C140" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D140" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F140" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G140" s="19">
-        <v>1353996.87734464</v>
-      </c>
-      <c r="H140" s="20">
-        <v>0.9999999999948527</v>
-      </c>
-      <c r="I140" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J140" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" ht="15" customHeight="1">
-      <c r="B143" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="C143" s="22"/>
-      <c r="D143" s="22"/>
-      <c r="E143" s="22"/>
-      <c r="F143" s="22"/>
-      <c r="G143" s="22"/>
-      <c r="H143" s="22"/>
-      <c r="I143" s="22"/>
-    </row>
-    <row r="144" spans="2:8" ht="15" customHeight="1">
-      <c r="B144" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="C144" s="22"/>
-      <c r="D144" s="22"/>
-      <c r="E144" s="22"/>
-      <c r="F144" s="22"/>
-      <c r="G144" s="22"/>
-      <c r="H144" s="22"/>
-    </row>
-    <row r="145" spans="2:8" ht="15" customHeight="1">
-      <c r="B145" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="C145" s="22"/>
-      <c r="D145" s="22"/>
-      <c r="E145" s="22"/>
-      <c r="F145" s="22"/>
-      <c r="G145" s="22"/>
-      <c r="H145" s="22"/>
-    </row>
-    <row r="146" spans="2:8" ht="15" customHeight="1">
-      <c r="B146" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="C146" s="22"/>
-      <c r="D146" s="22"/>
-      <c r="E146" s="22"/>
-      <c r="F146" s="22"/>
-      <c r="G146" s="22"/>
-      <c r="H146" s="22"/>
-    </row>
-    <row r="147" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B147" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="C147" s="22"/>
-      <c r="D147" s="22"/>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
-      <c r="G147" s="22"/>
-      <c r="H147" s="22"/>
-    </row>
-    <row r="148" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B148" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C148" s="22"/>
-      <c r="D148" s="22"/>
-      <c r="E148" s="22"/>
-      <c r="F148" s="22"/>
-      <c r="G148" s="22"/>
-      <c r="H148" s="22"/>
-    </row>
-    <row r="149" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B149" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="22"/>
-    </row>
-    <row r="150" spans="2:7" ht="51.75" customHeight="1">
-      <c r="B150" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C150" s="24"/>
-      <c r="D150" s="24"/>
-      <c r="E150" s="24"/>
-      <c r="F150" s="24"/>
-      <c r="G150" s="24"/>
-    </row>
-    <row r="153" ht="15">
-      <c r="B153" s="22" t="s">
+      <c r="B140" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J140" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" ht="15" customHeight="1">
+      <c r="B141" s="19" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="168" ht="15">
-      <c r="B168" s="22" t="s">
+      <c r="C141" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="20">
+        <v>28110.40878449031</v>
+      </c>
+      <c r="H141" s="21">
+        <v>0.018763545589244254</v>
+      </c>
+      <c r="I141" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J141" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" ht="15" customHeight="1">
+      <c r="B142" s="19" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="169" ht="15">
-      <c r="B169" s="22" t="s">
+      <c r="C142" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D142" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" s="20">
+        <v>1498139.49878449</v>
+      </c>
+      <c r="H142" s="21">
+        <v>0.9999999999950442</v>
+      </c>
+      <c r="I142" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J142" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" ht="15" customHeight="1">
+      <c r="B143" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D143" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J143" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" ht="15" customHeight="1">
+      <c r="B144" s="19" t="s">
         <v>217</v>
       </c>
+      <c r="C144" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" s="20">
+        <v>-235000</v>
+      </c>
+      <c r="H144" s="21">
+        <v>-0.15686122700233618</v>
+      </c>
+      <c r="I144" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J144" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" ht="15" customHeight="1">
+      <c r="B145" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H145" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I145" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J145" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="2:10" ht="15" customHeight="1">
+      <c r="B146" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H146" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J146" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="2:10" ht="15" customHeight="1">
+      <c r="B147" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H147" s="17">
+        <v>-0.0033374729149433222</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J147" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" ht="15" customHeight="1">
+      <c r="B148" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G148" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H148" s="17">
+        <v>-0.0033374729149433222</v>
+      </c>
+      <c r="I148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J148" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" ht="15" customHeight="1">
+      <c r="B149" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H149" s="17">
+        <v>-0.0033374729149433222</v>
+      </c>
+      <c r="I149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J149" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" ht="15" customHeight="1">
+      <c r="B150" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H150" s="17">
+        <v>-0.005006209372414984</v>
+      </c>
+      <c r="I150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J150" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="2:10" ht="15" customHeight="1">
+      <c r="B151" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G151" s="16">
+        <v>-2500</v>
+      </c>
+      <c r="H151" s="17">
+        <v>-0.0016687364574716611</v>
+      </c>
+      <c r="I151" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J151" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" ht="15" customHeight="1">
+      <c r="B152" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H152" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" ht="15" customHeight="1">
+      <c r="B153" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G153" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H153" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" ht="15" customHeight="1">
+      <c r="B154" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H154" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J154" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" ht="15" customHeight="1">
+      <c r="B155" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H155" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" ht="15" customHeight="1">
+      <c r="B156" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H156" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J156" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10" ht="15" customHeight="1">
+      <c r="B157" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H157" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J157" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="2:10" ht="15" customHeight="1">
+      <c r="B158" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H158" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J158" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" spans="2:10" ht="15" customHeight="1">
+      <c r="B159" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H159" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J159" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" ht="15" customHeight="1">
+      <c r="B160" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H160" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J160" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" ht="15" customHeight="1">
+      <c r="B161" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H161" s="17">
+        <v>-0.005006209372414984</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J161" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" ht="15" customHeight="1">
+      <c r="B162" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="16">
+        <v>-2500</v>
+      </c>
+      <c r="H162" s="17">
+        <v>-0.0016687364574716611</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J162" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" ht="15" customHeight="1">
+      <c r="B163" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H163" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1">
+      <c r="B164" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H164" s="17">
+        <v>-0.0033374729149433222</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" ht="15" customHeight="1">
+      <c r="B165" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H165" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J165" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" ht="15" customHeight="1">
+      <c r="B166" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H166" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J166" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" ht="15" customHeight="1">
+      <c r="B167" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H167" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="15" customHeight="1">
+      <c r="B168" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H168" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I168" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J168" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="15" customHeight="1">
+      <c r="B169" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H169" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J169" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="15" customHeight="1">
+      <c r="B170" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H170" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J170" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" ht="15" customHeight="1">
+      <c r="B171" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H171" s="17">
+        <v>-0.0033374729149433222</v>
+      </c>
+      <c r="I171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J171" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" ht="15" customHeight="1">
+      <c r="B172" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H172" s="17">
+        <v>-0.0066749458298866445</v>
+      </c>
+      <c r="I172" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J172" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" ht="15" customHeight="1">
+      <c r="B173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I173" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J173" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9" ht="15" customHeight="1">
+      <c r="B176" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C176" s="24"/>
+      <c r="D176" s="24"/>
+      <c r="E176" s="24"/>
+      <c r="F176" s="24"/>
+      <c r="G176" s="24"/>
+      <c r="H176" s="24"/>
+      <c r="I176" s="24"/>
+    </row>
+    <row r="177" spans="2:8" ht="15" customHeight="1">
+      <c r="B177" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C177" s="24"/>
+      <c r="D177" s="24"/>
+      <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24"/>
+    </row>
+    <row r="178" spans="2:8" ht="15" customHeight="1">
+      <c r="B178" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C178" s="24"/>
+      <c r="D178" s="24"/>
+      <c r="E178" s="24"/>
+      <c r="F178" s="24"/>
+      <c r="G178" s="24"/>
+      <c r="H178" s="24"/>
+    </row>
+    <row r="179" spans="2:8" ht="15" customHeight="1">
+      <c r="B179" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C179" s="24"/>
+      <c r="D179" s="24"/>
+      <c r="E179" s="24"/>
+      <c r="F179" s="24"/>
+      <c r="G179" s="24"/>
+      <c r="H179" s="24"/>
+    </row>
+    <row r="180" spans="2:8" ht="15" customHeight="1">
+      <c r="B180" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C180" s="24"/>
+      <c r="D180" s="24"/>
+      <c r="E180" s="24"/>
+      <c r="F180" s="24"/>
+      <c r="G180" s="24"/>
+      <c r="H180" s="24"/>
+    </row>
+    <row r="181" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B181" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="C181" s="24"/>
+      <c r="D181" s="24"/>
+      <c r="E181" s="24"/>
+      <c r="F181" s="24"/>
+      <c r="G181" s="24"/>
+      <c r="H181" s="24"/>
+    </row>
+    <row r="182" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B182" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="C182" s="24"/>
+      <c r="D182" s="24"/>
+      <c r="E182" s="24"/>
+      <c r="F182" s="24"/>
+      <c r="G182" s="24"/>
+      <c r="H182" s="24"/>
+    </row>
+    <row r="183" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B183" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="C183" s="24"/>
+      <c r="D183" s="24"/>
+      <c r="E183" s="24"/>
+      <c r="F183" s="24"/>
+      <c r="G183" s="24"/>
+      <c r="H183" s="24"/>
+    </row>
+    <row r="184" spans="2:7" ht="55.5" customHeight="1">
+      <c r="B184" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+    </row>
+    <row r="187" ht="15">
+      <c r="B187" s="24" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="202" ht="15">
+      <c r="B202" s="24" t="s">
+        <v>244</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B150:G150"/>
-    <mergeCell ref="B145:H145"/>
-    <mergeCell ref="B146:H146"/>
-    <mergeCell ref="B147:H147"/>
-    <mergeCell ref="B148:H148"/>
-    <mergeCell ref="B149:H149"/>
+  <mergeCells count="12">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B143:I143"/>
-    <mergeCell ref="B144:H144"/>
+    <mergeCell ref="B176:I176"/>
+    <mergeCell ref="B177:H177"/>
+    <mergeCell ref="B183:H183"/>
+    <mergeCell ref="B184:G184"/>
+    <mergeCell ref="B178:H178"/>
+    <mergeCell ref="B179:H179"/>
+    <mergeCell ref="B180:H180"/>
+    <mergeCell ref="B181:H181"/>
+    <mergeCell ref="B182:H182"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
